--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487886_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487886_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6975</v>
+        <v>7.5269</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1399</v>
+        <v>4.6757</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5576</v>
+        <v>2.8512</v>
       </c>
       <c r="G2" t="n">
         <v>5.7752</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5345</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.162</v>
+        <v>-0.6262</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3725</v>
+        <v>-0.0789</v>
       </c>
       <c r="V2" t="n">
         <v>0.5838</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9332</v>
+        <v>2.2817</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2987</v>
+        <v>0.4711</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6345</v>
+        <v>1.8106</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5109</v>
@@ -688,13 +688,13 @@
         <v>2.2893</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.5622</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0867</v>
+        <v>0.2591</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.8213</v>
       </c>
       <c r="V3" t="n">
         <v>1.2737</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. PAREJO CAMACHO</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3605</v>
+        <v>1.2271</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0392</v>
+        <v>-0.2537</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3212</v>
+        <v>1.4808</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2837</v>
+        <v>1.2462</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3114</v>
+        <v>0.3498</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0278</v>
+        <v>0.8964</v>
       </c>
       <c r="J4" t="n">
-        <v>0.443</v>
+        <v>0.4421</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3646</v>
+        <v>0.403</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0784</v>
+        <v>0.0392</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1593</v>
+        <v>0.8041</v>
       </c>
       <c r="N4" t="n">
         <v>-0.0532</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1061</v>
+        <v>0.8572</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6824</v>
+        <v>0.3347</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.1148</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0861</v>
+        <v>0.2199</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.23</v>
+        <v>-0.3538</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.23</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>L. PAREJO CAMACHO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8602</v>
+        <v>0.9677</v>
       </c>
       <c r="E5" t="n">
-        <v>2.071</v>
+        <v>0.6758</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2108</v>
+        <v>0.2919</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3628</v>
+        <v>0.2837</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8508</v>
+        <v>0.3114</v>
       </c>
       <c r="I5" t="n">
-        <v>1.512</v>
+        <v>-0.0278</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0771</v>
+        <v>0.443</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.431</v>
+        <v>0.3646</v>
       </c>
       <c r="L5" t="n">
-        <v>2.508</v>
+        <v>0.0784</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2857</v>
+        <v>-0.1593</v>
       </c>
       <c r="N5" t="n">
-        <v>1.2817</v>
+        <v>-0.0532</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.996</v>
+        <v>-0.1061</v>
       </c>
       <c r="P5" t="n">
         <v>0.6244</v>
@@ -844,28 +844,28 @@
         <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2081</v>
+        <v>0.2897</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3477</v>
+        <v>0.2329</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1396</v>
+        <v>0.0568</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.3351</v>
+        <v>-0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.9813</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7039</v>
+        <v>0.753</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7476</v>
+        <v>1.9638</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4514</v>
+        <v>-1.2108</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2462</v>
+        <v>2.3628</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3498</v>
+        <v>0.8508</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8964</v>
+        <v>1.512</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4421</v>
+        <v>2.0771</v>
       </c>
       <c r="K6" t="n">
-        <v>0.403</v>
+        <v>-0.431</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0392</v>
+        <v>2.508</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8041</v>
+        <v>0.2857</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0532</v>
+        <v>1.2817</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8572</v>
+        <v>-0.996</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1885</v>
+        <v>0.101</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3791</v>
+        <v>0.2405</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1905</v>
+        <v>-0.1396</v>
       </c>
       <c r="V6" t="n">
+        <v>-2.3351</v>
+      </c>
+      <c r="W6" t="n">
         <v>-0.3538</v>
       </c>
-      <c r="W6" t="n">
-        <v>0.23</v>
-      </c>
       <c r="X6" t="n">
-        <v>-0.5838</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>J. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5365</v>
+        <v>0.5629</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8108</v>
+        <v>1.7204</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2743</v>
+        <v>-1.1576</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0425</v>
+        <v>4.6534</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3029</v>
+        <v>2.8507</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7397</v>
+        <v>1.8027</v>
       </c>
       <c r="J7" t="n">
-        <v>1.357</v>
+        <v>4.3393</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6908</v>
+        <v>2.0059</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6662</v>
+        <v>2.3333</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3144</v>
+        <v>0.3141</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3879</v>
+        <v>0.8448</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0735</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2081</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2487</v>
+        <v>-2.2893</v>
       </c>
       <c r="R7" t="n">
         <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3909</v>
+        <v>-0.3392</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1802</v>
+        <v>-0.3295</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2108</v>
+        <v>-0.0097</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1051</v>
+        <v>-2.9188</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.4776</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.6275</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MARIN ORTEGA</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4572</v>
+        <v>0.0827</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2918</v>
+        <v>-0.1232</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8346</v>
+        <v>0.206</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6534</v>
+        <v>1.0133</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8507</v>
+        <v>-0.0236</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8027</v>
+        <v>1.0369</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3393</v>
+        <v>-0.1785</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0059</v>
+        <v>-0.9623</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3333</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3141</v>
+        <v>1.1918</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8448</v>
+        <v>0.9387</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5306999999999999</v>
+        <v>0.2531</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8325</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2893</v>
+        <v>-2.0812</v>
       </c>
       <c r="R8" t="n">
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4449</v>
+        <v>-0.4123</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7581</v>
+        <v>-0.3047</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3132</v>
+        <v>-0.1076</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.9188</v>
+        <v>0.1061</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.4412</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.9188</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1121</v>
+        <v>-0.1586</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1232</v>
+        <v>0.2331</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2353</v>
+        <v>-0.3917</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0133</v>
+        <v>1.0425</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0236</v>
+        <v>0.3029</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0369</v>
+        <v>0.7397</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1785</v>
+        <v>1.357</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9623</v>
+        <v>0.6908</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.6662</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1918</v>
+        <v>-0.3144</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9387</v>
+        <v>-0.3879</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2531</v>
+        <v>0.0735</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0812</v>
+        <v>-1.2487</v>
       </c>
       <c r="R9" t="n">
         <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.383</v>
+        <v>0.6958</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3047</v>
+        <v>0.6025</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1061</v>
+        <v>-2.1051</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4412</v>
+        <v>-0.4776</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3351</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ CALZADO</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9715</v>
+        <v>-0.9647</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7796</v>
+        <v>-2.4244</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1919</v>
+        <v>1.4598</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9063</v>
+        <v>1.422</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1919</v>
+        <v>0.4538</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7144</v>
+        <v>0.9683</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7144</v>
+        <v>0.6711</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.8458</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7144</v>
+        <v>-0.1747</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1919</v>
+        <v>0.7509</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1919</v>
+        <v>-0.3921</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.143</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.4458</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0262</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.4195</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>D. RODRIGUEZ CALZADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1723</v>
+        <v>-0.9715</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2463</v>
+        <v>-0.7796</v>
       </c>
       <c r="F11" t="n">
-        <v>3.074</v>
+        <v>-0.1919</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.461</v>
+        <v>-0.9063</v>
       </c>
       <c r="H11" t="n">
-        <v>0.482</v>
+        <v>-0.1919</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9431</v>
+        <v>-0.7144</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9752</v>
+        <v>-0.7144</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.028</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9472</v>
+        <v>-0.7144</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5141</v>
+        <v>-0.1919</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5101</v>
+        <v>-0.1919</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0041</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.3299</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0812</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8298</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0588</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2289</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.383</v>
+        <v>-1.8469</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9602</v>
+        <v>-5.0383</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5772</v>
+        <v>3.1914</v>
       </c>
       <c r="G12" t="n">
-        <v>1.422</v>
+        <v>-1.461</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4538</v>
+        <v>0.482</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9683</v>
+        <v>-1.9431</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6711</v>
+        <v>-1.9752</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8458</v>
+        <v>-0.028</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1747</v>
+        <v>-1.9472</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7509</v>
+        <v>0.5141</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3921</v>
+        <v>0.5101</v>
       </c>
       <c r="O12" t="n">
-        <v>1.143</v>
+        <v>0.0041</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.6649</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1218</v>
+        <v>-3.3299</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0274</v>
+        <v>0.1553</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.2668</v>
       </c>
       <c r="U12" t="n">
-        <v>0.537</v>
+        <v>-0.1115</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1675</v>
+        <v>0.7076</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1675</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="13">
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.134299999999996</v>
+        <v>9.460299999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7944999999999998</v>
+        <v>1.120699999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>8.339599999999999</v>
+        <v>8.339699999999999</v>
       </c>
       <c r="G13" t="n">
         <v>14.9209</v>
       </c>
       <c r="H13" t="n">
-        <v>8.858999999999996</v>
+        <v>8.858999999999998</v>
       </c>
       <c r="I13" t="n">
-        <v>6.0619</v>
+        <v>6.061900000000001</v>
       </c>
       <c r="J13" t="n">
         <v>10.5343</v>
@@ -1468,16 +1468,16 @@
         <v>14.5683</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3883000000000001</v>
+        <v>-0.06170000000000003</v>
       </c>
       <c r="T13" t="n">
-        <v>0.09099999999999997</v>
+        <v>0.4172</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4791000000000002</v>
+        <v>-0.4790999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.4391</v>
+        <v>-6.439100000000001</v>
       </c>
       <c r="W13" t="n">
         <v>3.6973</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0122</v>
+        <v>8.6401</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0429</v>
+        <v>7.0073</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9693000000000001</v>
+        <v>1.6328</v>
       </c>
       <c r="G14" t="n">
         <v>1.1749</v>
@@ -1546,13 +1546,13 @@
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2226</v>
+        <v>0.4053</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9539</v>
+        <v>0.0105</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2687</v>
+        <v>0.3948</v>
       </c>
       <c r="V14" t="n">
         <v>6.4356</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3414</v>
+        <v>2.8105</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8902</v>
+        <v>2.5687</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4512</v>
+        <v>0.2418</v>
       </c>
       <c r="G15" t="n">
         <v>2.0914</v>
@@ -1624,13 +1624,13 @@
         <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2094</v>
+        <v>-0.3215</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3295</v>
+        <v>-0.651</v>
       </c>
       <c r="U15" t="n">
-        <v>0.539</v>
+        <v>0.3295</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7663</v>
+        <v>1.3617</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3887</v>
+        <v>1.2816</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3776</v>
+        <v>0.0801</v>
       </c>
       <c r="G16" t="n">
         <v>0.4286</v>
@@ -1702,13 +1702,13 @@
         <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4647</v>
+        <v>1.06</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4129</v>
+        <v>0.3058</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0517</v>
+        <v>0.7542</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1675</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. DIENE</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1689</v>
+        <v>-1.4422</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1355</v>
+        <v>-1.9386</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9666</v>
+        <v>0.4964</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.889</v>
+        <v>-4.8316</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.582</v>
+        <v>-1.6761</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.307</v>
+        <v>-3.1555</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2152</v>
+        <v>-3.37</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3328</v>
+        <v>-1.4228</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1176</v>
+        <v>-1.9472</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6737</v>
+        <v>-1.4616</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2492</v>
+        <v>-0.2533</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4245</v>
+        <v>-1.2083</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.9137</v>
+        <v>2.0812</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.1624</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487</v>
+        <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2221</v>
+        <v>0.6041</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0746</v>
+        <v>0.0339</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1475</v>
+        <v>0.5703</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4117</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1675</v>
+        <v>1.3975</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2441</v>
+        <v>-0.6934</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2769</v>
+        <v>-1.7078</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4898</v>
+        <v>-2.3827</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2129</v>
+        <v>0.6748</v>
       </c>
       <c r="G18" t="n">
         <v>-2.8132</v>
@@ -1858,13 +1858,13 @@
         <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>0.518</v>
+        <v>1.087</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5401</v>
+        <v>0.6473</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0221</v>
+        <v>0.4398</v>
       </c>
       <c r="V18" t="n">
         <v>0.2264</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>P. DIENE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.644</v>
+        <v>-2.3349</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7959</v>
+        <v>-3.5285</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1519</v>
+        <v>1.1937</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.8316</v>
+        <v>-1.889</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6761</v>
+        <v>-1.582</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.1555</v>
+        <v>-0.307</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.37</v>
+        <v>-1.2152</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4228</v>
+        <v>-1.3328</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9472</v>
+        <v>0.1176</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4616</v>
+        <v>-0.6737</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2533</v>
+        <v>-0.2492</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2083</v>
+        <v>-0.4245</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0812</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-4.1624</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0812</v>
+        <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5976</v>
+        <v>1.0561</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8234</v>
+        <v>0.6815</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2258</v>
+        <v>0.3745</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7040999999999999</v>
+        <v>1.4117</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3975</v>
+        <v>1.1675</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6934</v>
+        <v>0.2441</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7895</v>
+        <v>-2.3531</v>
       </c>
       <c r="E20" t="n">
         <v>-2.2092</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5804</v>
+        <v>-0.1439</v>
       </c>
       <c r="G20" t="n">
         <v>0.2952</v>
@@ -2014,13 +2014,13 @@
         <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3792</v>
+        <v>-0.9427</v>
       </c>
       <c r="T20" t="n">
         <v>-0.7177</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6615</v>
+        <v>-0.225</v>
       </c>
       <c r="V20" t="n">
         <v>0.5838</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0226</v>
+        <v>-2.6322</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1544</v>
+        <v>-1.9401</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8683</v>
+        <v>-0.6921</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9842</v>
@@ -2092,13 +2092,13 @@
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.976</v>
+        <v>-0.5855</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5219</v>
+        <v>-0.3076</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4541</v>
+        <v>-0.2779</v>
       </c>
       <c r="V21" t="n">
         <v>0.9376</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1202</v>
+        <v>-4.0845</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4688</v>
+        <v>-2.576</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6514</v>
+        <v>-1.5085</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9395</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1553</v>
+        <v>-0.1195</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1924</v>
+        <v>0.0853</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3477</v>
+        <v>-0.2048</v>
       </c>
       <c r="V22" t="n">
         <v>-1.9848</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2321</v>
+        <v>-5.2488</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4081</v>
+        <v>-4.6224</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.824</v>
+        <v>-0.6263</v>
       </c>
       <c r="G23" t="n">
         <v>-5.4535</v>
@@ -2248,13 +2248,13 @@
         <v>1.6649</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3047</v>
+        <v>0.288</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6054</v>
+        <v>0.3911</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3007</v>
+        <v>-0.103</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7076</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.1343</v>
+        <v>-6.9912</v>
       </c>
       <c r="E24" t="n">
         <v>-8.3399</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7945999999999996</v>
+        <v>1.3488</v>
       </c>
       <c r="G24" t="n">
         <v>-14.9209</v>
@@ -2326,16 +2326,16 @@
         <v>13.5277</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3881999999999999</v>
+        <v>2.5313</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4790000000000005</v>
+        <v>0.4790999999999998</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.09079999999999994</v>
+        <v>2.0524</v>
       </c>
       <c r="V24" t="n">
-        <v>6.4393</v>
+        <v>6.439299999999998</v>
       </c>
       <c r="W24" t="n">
         <v>10.1362</v>
